--- a/product_import/Anandi_Sarees_Product_Upload_Template.xlsx
+++ b/product_import/Anandi_Sarees_Product_Upload_Template.xlsx
@@ -1,612 +1,313 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8622F997-E49F-44E7-B0FA-BE4A903B3B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Products" sheetId="1" r:id="rId1"/>
-    <sheet name="Reference (do not edit)" sheetId="2" r:id="rId2"/>
-    <sheet name="Instructions" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Products" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Reference (do not edit)" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Instructions" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
           <t>Unique product code, e.g. AS-PAITHANI-001</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
           <t>e.g. Yeola Pure Silk Paithani - Peacock Motif</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
           <t>Pick from dropdown</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
           <t>Pick from dropdown</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
           <t>e.g. Peacock Blue</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
           <t>Original price in Rs, e.g. 4999</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
           <t>Discounted/actual selling price in Rs</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
           <t>How many pieces in stock</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
           <t>e.g. 6.3</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
           <t>One-line summary shown on product cards</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
           <t>Full product description (optional, can Generate with AI later)</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
           <t>e.g. Dry clean only</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Exact file name of the photo in the images folder, e.g. paithani-001.jpg</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <t>Insert a picture directly into this cell (Insert &gt; Pictures &gt; Place in Cell). First photo becomes the main image.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO - shows in Featured section</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="R1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="S1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="T1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
           <t>YES or NO</t>
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Example row - replace with your real product, or delete this row</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+    <comment ref="A2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0">
+      <text>
+        <r>
+          <t>Example row - replace with your real product, or delete this row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U2" authorId="0">
+      <text>
+        <r>
           <t>Example row - replace with your real product, or delete this row</t>
         </r>
       </text>
@@ -616,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="97">
   <si>
     <t>SKU*</t>
   </si>
@@ -660,7 +361,7 @@
     <t>Handloom</t>
   </si>
   <si>
-    <t>Image File Name</t>
+    <t>Product Photo</t>
   </si>
   <si>
     <t>Featured</t>
@@ -708,9 +409,6 @@
     <t>YES</t>
   </si>
   <si>
-    <t>paithani-001.jpg</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -873,13 +571,16 @@
     <t>3. For Blouse Included, Handloom, and all the Featured/New Arrival/etc columns, type YES or NO.</t>
   </si>
   <si>
-    <t>4. Put product photos in a folder named 'images' next to this Excel file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   In the 'Image File Name' column, type the exact file name (e.g. paithani-001.jpg).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   You can list multiple images for one product separated by a comma, e.g. paithani-001.jpg, paithani-001-b.jpg</t>
+    <t>4. To add a photo: click the 'Product Photo' cell for that row, then in Excel go to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Insert &gt; Pictures &gt; This Device, pick the photo, and Excel will place it in that cell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (If it doesn't land inside the cell, right-click the picture &gt; Size and Properties &gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   set 'Move and size with cells'.) One photo per row becomes that product's main image.</t>
   </si>
   <si>
     <t>5. Delete the example row (row 2) once you understand the format, or overwrite it with a real product.</t>
@@ -888,7 +589,7 @@
     <t>6. SKU must be unique for every product - use your own numbering, e.g. AS-PAITHANI-001, AS-PAITHANI-002...</t>
   </si>
   <si>
-    <t>7. Save the file and send it back along with the images folder - it will be uploaded directly.</t>
+    <t>7. Save the file and upload it directly from the admin panel: Products &gt; Import from Excel.</t>
   </si>
   <si>
     <t>Notes:</t>
@@ -901,41 +602,40 @@
   </si>
   <si>
     <t>- Description can be left blank - it can be generated later from the admin panel using 'Generate with AI'</t>
+  </si>
+  <si>
+    <t>- A product photo is optional but recommended - rows without one are still created, just with no image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  until you add one later from the admin panel.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF999999"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF999999"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1309,9 +1009,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U201"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -1325,13 +1025,13 @@
     <col min="12" max="12" width="28" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="16" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="34" customHeight="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1396,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="90" customHeight="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1440,347 +1140,572 @@
         <v>29</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="90" customHeight="1" spans="3:21" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid category" error="Please pick a category from the dropdown list." sqref="C10:C201">
+      <formula1>"Paithani Sarees,Nauvari Sarees (9 Yards),Peshwai Sarees,Narayan Peth Sarees,Solapuri Cotton Sarees,Ilkal Sarees,Khun Fabric Sarees,Maharashtrian Bridal Sarees,Maharashtrian Wedding Collection,Maharashtrian Festive Collection,Maharashtrian Haldi Collection,Maharashtrian Reception Collection,Maharashtrian Traditional Wear,Banarasi Silk,Kanjivaram Silk,Patola,Bandhani,Chanderi,Maheshwari,Kota Doria,Tussar Silk,Organza,Linen,Cotton,Georgette,Chiffon,Crepe,Satin Silk,Soft Silk,Tissue Silk,Handloom Collection,Printed Sarees,Embroidered Sarees,Party Wear Sarees,Office Wear Sarees,Casual Wear Sarees,Designer Sarees,Wedding Collection,Festive Collection,Luxury Collection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid category" error="Please pick a category from the dropdown list." sqref="C2:C201">
+      <formula1>"Paithani Sarees,Nauvari Sarees (9 Yards),Peshwai Sarees,Narayan Peth Sarees,Solapuri Cotton Sarees,Ilkal Sarees,Khun Fabric Sarees,Maharashtrian Bridal Sarees,Maharashtrian Wedding Collection,Maharashtrian Festive Collection,Maharashtrian Haldi Collection,Maharashtrian Reception Collection,Maharashtrian Traditional Wear,Banarasi Silk,Kanjivaram Silk,Patola,Bandhani,Chanderi,Maheshwari,Kota Doria,Tussar Silk,Organza,Linen,Cotton,Georgette,Chiffon,Crepe,Satin Silk,Soft Silk,Tissue Silk,Handloom Collection,Printed Sarees,Embroidered Sarees,Party Wear Sarees,Office Wear Sarees,Casual Wear Sarees,Designer Sarees,Wedding Collection,Festive Collection,Luxury Collection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid fabric" error="Please pick a fabric from the dropdown list." sqref="D10:D201">
+      <formula1>"Pure Silk,Semi Silk,Cotton,Cotton Silk,Linen,Organza,Chiffon,Georgette,Tissue,Tussar Silk,Banarasi Silk,Kanjivaram Silk,Khun Fabric,Modal Silk,Crepe,Satin,Art Silk"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid fabric" error="Please pick a fabric from the dropdown list." sqref="D2:D201">
+      <formula1>"Pure Silk,Semi Silk,Cotton,Cotton Silk,Linen,Organza,Chiffon,Georgette,Tissue,Tussar Silk,Banarasi Silk,Kanjivaram Silk,Khun Fabric,Modal Silk,Crepe,Satin,Art Silk"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M10:N201">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M2:N201">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="P10:U201">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="P2:U201">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>48</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>49</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>54</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>59</v>
       </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>61</v>
       </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>62</v>
       </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
         <v>66</v>
       </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>67</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>69</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
       </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="C21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
         <v>74</v>
       </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
         <v>75</v>
       </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
         <v>77</v>
       </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
         <v>78</v>
       </c>
-      <c r="C26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
@@ -1788,100 +1713,115 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>